--- a/010_input/assembled_measures_test.xlsx
+++ b/010_input/assembled_measures_test.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="27" documentId="8_{6B63D2C0-3DE8-4A2E-A6B0-A44E8664126A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{586FD095-555A-48E8-A3F7-2A1C067D891C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="7305" yWindow="1035" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12892,15 +12892,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B011C3FEFFEFCF44990405A8404263A2" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ff8dfd3bc83a02ed6a3437faf473449a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8a600ae29b0fcdec2bdff655f54bd0a0" ns2:_="">
     <xsd:import namespace="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
@@ -13044,6 +13035,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D8206A-3930-49CF-9012-9CF437EACA17}">
   <ds:schemaRefs>
@@ -13054,14 +13054,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7742BE60-C810-4388-81AC-BF19576EDDBE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59620F56-1850-40FD-8DCB-EB3678619526}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13077,4 +13069,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7742BE60-C810-4388-81AC-BF19576EDDBE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>